--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1008"/>
+  <dimension ref="A1:Z1011"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58050,14 +58050,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 2388-2024</t>
+          <t>A 2382-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58070,7 +58070,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -58107,14 +58107,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 2382-2024</t>
+          <t>A 2388-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58127,7 +58127,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -58171,7 +58171,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58278,14 +58278,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 3035-2024</t>
+          <t>A 3128-2024</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -58335,14 +58335,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 3129-2024</t>
+          <t>A 3035-2024</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58355,7 +58355,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -58392,14 +58392,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 3128-2024</t>
+          <t>A 3129-2024</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -58449,14 +58449,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 3653-2024</t>
+          <t>A 3654-2024</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58506,14 +58506,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 3654-2024</t>
+          <t>A 3653-2024</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58526,7 +58526,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58570,7 +58570,7 @@
         <v>45322</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45327</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58734,14 +58734,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 4676-2024</t>
+          <t>A 4670-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58791,14 +58791,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 4670-2024</t>
+          <t>A 4676-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58855,7 +58855,7 @@
         <v>45328</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58912,7 +58912,7 @@
         <v>45328</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58969,7 +58969,7 @@
         <v>45328</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>45328</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59083,7 +59083,7 @@
         <v>45329</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45330</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45331</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45331</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45334</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59358,7 +59358,7 @@
       </c>
       <c r="R1007" s="2" t="inlineStr"/>
     </row>
-    <row r="1008">
+    <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
           <t>A 6047-2024</t>
@@ -59368,7 +59368,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59414,6 +59414,182 @@
         <v>0</v>
       </c>
       <c r="R1008" s="2" t="inlineStr"/>
+    </row>
+    <row r="1009" ht="15" customHeight="1">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>A 6242-2024</t>
+        </is>
+      </c>
+      <c r="B1009" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C1009" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>RONNEBY</t>
+        </is>
+      </c>
+      <c r="G1009" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1009" s="2" t="inlineStr"/>
+    </row>
+    <row r="1010" ht="15" customHeight="1">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>A 6248-2024</t>
+        </is>
+      </c>
+      <c r="B1010" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C1010" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>RONNEBY</t>
+        </is>
+      </c>
+      <c r="G1010" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1010" s="2" t="inlineStr"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>A 6266-2024</t>
+        </is>
+      </c>
+      <c r="B1011" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C1011" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>RONNEBY</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G1011" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1011" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1011"/>
+  <dimension ref="A1:Z1012"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58278,14 +58278,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 3128-2024</t>
+          <t>A 3035-2024</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -58335,14 +58335,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 3035-2024</t>
+          <t>A 3128-2024</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58355,7 +58355,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -58399,7 +58399,7 @@
         <v>45316</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45321</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45321</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45322</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45327</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>45328</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58791,14 +58791,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 4676-2024</t>
+          <t>A 4675-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58848,14 +58848,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 4665-2024</t>
+          <t>A 4676-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58868,7 +58868,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58905,14 +58905,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 4681-2024</t>
+          <t>A 4665-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58962,14 +58962,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 4728-2024</t>
+          <t>A 4681-2024</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -59019,14 +59019,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4675-2024</t>
+          <t>A 4728-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59083,7 +59083,7 @@
         <v>45329</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45330</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45331</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45331</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45334</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59425,7 +59425,7 @@
         <v>45337</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59475,14 +59475,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 6248-2024</t>
+          <t>A 6266-2024</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59494,8 +59494,13 @@
           <t>RONNEBY</t>
         </is>
       </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1010" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -59529,67 +59534,119 @@
       </c>
       <c r="R1010" s="2" t="inlineStr"/>
     </row>
-    <row r="1011">
+    <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 6266-2024</t>
+          <t>A 6248-2024</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1011" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>RONNEBY</t>
+        </is>
+      </c>
+      <c r="G1011" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1011" s="2" t="inlineStr"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>A 6450-2024</t>
+        </is>
+      </c>
+      <c r="B1012" s="1" t="n">
         <v>45338</v>
       </c>
-      <c r="D1011" t="inlineStr">
-        <is>
-          <t>BLEKINGE LÄN</t>
-        </is>
-      </c>
-      <c r="E1011" t="inlineStr">
-        <is>
-          <t>RONNEBY</t>
-        </is>
-      </c>
-      <c r="F1011" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="G1011" t="n">
-        <v>2</v>
-      </c>
-      <c r="H1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="P1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="R1011" s="2" t="inlineStr"/>
+      <c r="C1012" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>RONNEBY</t>
+        </is>
+      </c>
+      <c r="G1012" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1012" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1012"/>
+  <dimension ref="A1:Z1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58285,7 +58285,7 @@
         <v>45316</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45316</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45316</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45321</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45321</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45322</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45327</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>45328</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58798,7 +58798,7 @@
         <v>45328</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58855,7 +58855,7 @@
         <v>45328</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58905,14 +58905,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 4665-2024</t>
+          <t>A 4728-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58962,14 +58962,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 4681-2024</t>
+          <t>A 4665-2024</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -59019,14 +59019,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4728-2024</t>
+          <t>A 4681-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59083,7 +59083,7 @@
         <v>45329</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45330</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45331</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45331</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45334</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59425,7 +59425,7 @@
         <v>45337</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59475,14 +59475,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 6266-2024</t>
+          <t>A 6248-2024</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59494,13 +59494,8 @@
           <t>RONNEBY</t>
         </is>
       </c>
-      <c r="F1010" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G1010" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -59537,14 +59532,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 6248-2024</t>
+          <t>A 6266-2024</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59556,8 +59551,13 @@
           <t>RONNEBY</t>
         </is>
       </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1011" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -59591,7 +59591,7 @@
       </c>
       <c r="R1011" s="2" t="inlineStr"/>
     </row>
-    <row r="1012">
+    <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
           <t>A 6450-2024</t>
@@ -59601,7 +59601,7 @@
         <v>45338</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59647,6 +59647,120 @@
         <v>0</v>
       </c>
       <c r="R1012" s="2" t="inlineStr"/>
+    </row>
+    <row r="1013" ht="15" customHeight="1">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>A 6660-2024</t>
+        </is>
+      </c>
+      <c r="B1013" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C1013" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>RONNEBY</t>
+        </is>
+      </c>
+      <c r="G1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1013" s="2" t="inlineStr"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>A 6869-2024</t>
+        </is>
+      </c>
+      <c r="B1014" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C1014" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>RONNEBY</t>
+        </is>
+      </c>
+      <c r="G1014" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1014" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58285,7 +58285,7 @@
         <v>45316</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45316</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45316</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45321</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45321</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45322</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58620,14 +58620,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 4411-2024</t>
+          <t>A 4469-2024</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58677,14 +58677,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 4469-2024</t>
+          <t>A 4411-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58734,14 +58734,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 4670-2024</t>
+          <t>A 4676-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58798,7 +58798,7 @@
         <v>45328</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58848,14 +58848,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 4676-2024</t>
+          <t>A 4665-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58868,7 +58868,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58905,14 +58905,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 4728-2024</t>
+          <t>A 4681-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58962,14 +58962,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 4665-2024</t>
+          <t>A 4670-2024</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -59019,14 +59019,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4681-2024</t>
+          <t>A 4728-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59083,7 +59083,7 @@
         <v>45329</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45330</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45331</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45331</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45334</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59425,7 +59425,7 @@
         <v>45337</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59482,7 +59482,7 @@
         <v>45337</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>45337</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>45338</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45341</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>45342</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58285,7 +58285,7 @@
         <v>45316</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45316</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45316</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45321</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45321</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45322</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58620,14 +58620,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 4469-2024</t>
+          <t>A 4411-2024</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58677,14 +58677,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 4411-2024</t>
+          <t>A 4469-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58734,14 +58734,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 4676-2024</t>
+          <t>A 4670-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58798,7 +58798,7 @@
         <v>45328</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58848,14 +58848,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 4665-2024</t>
+          <t>A 4728-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58868,7 +58868,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58905,14 +58905,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 4681-2024</t>
+          <t>A 4676-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58962,14 +58962,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 4670-2024</t>
+          <t>A 4665-2024</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -59019,14 +59019,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4728-2024</t>
+          <t>A 4681-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59083,7 +59083,7 @@
         <v>45329</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45330</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45331</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45331</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45334</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59418,14 +59418,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 6242-2024</t>
+          <t>A 6248-2024</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -59475,14 +59475,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 6248-2024</t>
+          <t>A 6266-2024</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59494,8 +59494,13 @@
           <t>RONNEBY</t>
         </is>
       </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1010" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -59532,14 +59537,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 6266-2024</t>
+          <t>A 6242-2024</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59551,13 +59556,8 @@
           <t>RONNEBY</t>
         </is>
       </c>
-      <c r="F1011" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G1011" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -59601,7 +59601,7 @@
         <v>45338</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45341</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>45342</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1014"/>
+  <dimension ref="A1:Z1016"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58278,14 +58278,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 3035-2024</t>
+          <t>A 3129-2024</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -58335,14 +58335,14 @@
     <row r="990" ht="15" customHeight="1">
       <c r="A990" t="inlineStr">
         <is>
-          <t>A 3128-2024</t>
+          <t>A 3035-2024</t>
         </is>
       </c>
       <c r="B990" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58355,7 +58355,7 @@
         </is>
       </c>
       <c r="G990" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="H990" t="n">
         <v>0</v>
@@ -58392,14 +58392,14 @@
     <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 3129-2024</t>
+          <t>A 3128-2024</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>
@@ -58449,14 +58449,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 3654-2024</t>
+          <t>A 3653-2024</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58506,14 +58506,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 3653-2024</t>
+          <t>A 3654-2024</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58526,7 +58526,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58570,7 +58570,7 @@
         <v>45322</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58620,14 +58620,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 4411-2024</t>
+          <t>A 4469-2024</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58677,14 +58677,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 4469-2024</t>
+          <t>A 4411-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58741,7 +58741,7 @@
         <v>45328</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58791,14 +58791,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 4675-2024</t>
+          <t>A 4676-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58855,7 +58855,7 @@
         <v>45328</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58905,14 +58905,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 4676-2024</t>
+          <t>A 4665-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58962,14 +58962,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 4665-2024</t>
+          <t>A 4681-2024</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -59019,14 +59019,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4681-2024</t>
+          <t>A 4675-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59083,7 +59083,7 @@
         <v>45329</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45330</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45331</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45331</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45334</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59418,14 +59418,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 6248-2024</t>
+          <t>A 6266-2024</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59437,8 +59437,13 @@
           <t>RONNEBY</t>
         </is>
       </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1009" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -59475,14 +59480,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 6266-2024</t>
+          <t>A 6248-2024</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59494,13 +59499,8 @@
           <t>RONNEBY</t>
         </is>
       </c>
-      <c r="F1010" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G1010" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -59544,7 +59544,7 @@
         <v>45337</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>45338</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45341</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
       </c>
       <c r="R1013" s="2" t="inlineStr"/>
     </row>
-    <row r="1014">
+    <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
           <t>A 6869-2024</t>
@@ -59715,7 +59715,7 @@
         <v>45342</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59761,6 +59761,120 @@
         <v>0</v>
       </c>
       <c r="R1014" s="2" t="inlineStr"/>
+    </row>
+    <row r="1015" ht="15" customHeight="1">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>A 7356-2024</t>
+        </is>
+      </c>
+      <c r="B1015" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C1015" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>RONNEBY</t>
+        </is>
+      </c>
+      <c r="G1015" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1015" s="2" t="inlineStr"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>A 7449-2024</t>
+        </is>
+      </c>
+      <c r="B1016" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C1016" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>BLEKINGE LÄN</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>RONNEBY</t>
+        </is>
+      </c>
+      <c r="G1016" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1016" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58285,7 +58285,7 @@
         <v>45316</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45316</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45316</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45321</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45321</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45322</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45327</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58734,14 +58734,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 4670-2024</t>
+          <t>A 4665-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58791,14 +58791,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 4676-2024</t>
+          <t>A 4681-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58848,14 +58848,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 4728-2024</t>
+          <t>A 4676-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58868,7 +58868,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58905,14 +58905,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 4665-2024</t>
+          <t>A 4728-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58962,14 +58962,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 4681-2024</t>
+          <t>A 4675-2024</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -59019,14 +59019,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4675-2024</t>
+          <t>A 4670-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59083,7 +59083,7 @@
         <v>45329</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45330</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45331</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45331</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45334</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59418,14 +59418,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 6266-2024</t>
+          <t>A 6248-2024</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59437,13 +59437,8 @@
           <t>RONNEBY</t>
         </is>
       </c>
-      <c r="F1009" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G1009" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -59480,14 +59475,14 @@
     <row r="1010" ht="15" customHeight="1">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>A 6248-2024</t>
+          <t>A 6266-2024</t>
         </is>
       </c>
       <c r="B1010" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59499,8 +59494,13 @@
           <t>RONNEBY</t>
         </is>
       </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1010" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -59544,7 +59544,7 @@
         <v>45337</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>45338</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45341</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>45342</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>45345</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59829,7 +59829,7 @@
         <v>45345</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58285,7 +58285,7 @@
         <v>45316</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45316</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45316</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58449,14 +58449,14 @@
     <row r="992" ht="15" customHeight="1">
       <c r="A992" t="inlineStr">
         <is>
-          <t>A 3653-2024</t>
+          <t>A 3654-2024</t>
         </is>
       </c>
       <c r="B992" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         </is>
       </c>
       <c r="G992" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H992" t="n">
         <v>0</v>
@@ -58506,14 +58506,14 @@
     <row r="993" ht="15" customHeight="1">
       <c r="A993" t="inlineStr">
         <is>
-          <t>A 3654-2024</t>
+          <t>A 3653-2024</t>
         </is>
       </c>
       <c r="B993" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58526,7 +58526,7 @@
         </is>
       </c>
       <c r="G993" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -58570,7 +58570,7 @@
         <v>45322</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45327</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58734,14 +58734,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 4665-2024</t>
+          <t>A 4676-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58791,14 +58791,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 4681-2024</t>
+          <t>A 4670-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58848,14 +58848,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 4676-2024</t>
+          <t>A 4728-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58868,7 +58868,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58905,14 +58905,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 4728-2024</t>
+          <t>A 4665-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58962,14 +58962,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 4675-2024</t>
+          <t>A 4681-2024</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -59019,14 +59019,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4670-2024</t>
+          <t>A 4675-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59083,7 +59083,7 @@
         <v>45329</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45330</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45331</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45331</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45334</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59418,14 +59418,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 6248-2024</t>
+          <t>A 6242-2024</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -59482,7 +59482,7 @@
         <v>45337</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59537,14 +59537,14 @@
     <row r="1011" ht="15" customHeight="1">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>A 6242-2024</t>
+          <t>A 6248-2024</t>
         </is>
       </c>
       <c r="B1011" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59557,7 +59557,7 @@
         </is>
       </c>
       <c r="G1011" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -59601,7 +59601,7 @@
         <v>45338</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45341</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>45342</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>45345</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59829,7 +59829,7 @@
         <v>45345</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45310</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58285,7 +58285,7 @@
         <v>45316</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45316</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45316</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45321</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45321</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45322</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58620,14 +58620,14 @@
     <row r="995" ht="15" customHeight="1">
       <c r="A995" t="inlineStr">
         <is>
-          <t>A 4469-2024</t>
+          <t>A 4411-2024</t>
         </is>
       </c>
       <c r="B995" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         </is>
       </c>
       <c r="G995" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -58677,14 +58677,14 @@
     <row r="996" ht="15" customHeight="1">
       <c r="A996" t="inlineStr">
         <is>
-          <t>A 4411-2024</t>
+          <t>A 4469-2024</t>
         </is>
       </c>
       <c r="B996" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         </is>
       </c>
       <c r="G996" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="H996" t="n">
         <v>0</v>
@@ -58734,14 +58734,14 @@
     <row r="997" ht="15" customHeight="1">
       <c r="A997" t="inlineStr">
         <is>
-          <t>A 4676-2024</t>
+          <t>A 4670-2024</t>
         </is>
       </c>
       <c r="B997" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         </is>
       </c>
       <c r="G997" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H997" t="n">
         <v>0</v>
@@ -58791,14 +58791,14 @@
     <row r="998" ht="15" customHeight="1">
       <c r="A998" t="inlineStr">
         <is>
-          <t>A 4670-2024</t>
+          <t>A 4675-2024</t>
         </is>
       </c>
       <c r="B998" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         </is>
       </c>
       <c r="G998" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -58848,14 +58848,14 @@
     <row r="999" ht="15" customHeight="1">
       <c r="A999" t="inlineStr">
         <is>
-          <t>A 4728-2024</t>
+          <t>A 4665-2024</t>
         </is>
       </c>
       <c r="B999" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58868,7 +58868,7 @@
         </is>
       </c>
       <c r="G999" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -58905,14 +58905,14 @@
     <row r="1000" ht="15" customHeight="1">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>A 4665-2024</t>
+          <t>A 4681-2024</t>
         </is>
       </c>
       <c r="B1000" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -58962,14 +58962,14 @@
     <row r="1001" ht="15" customHeight="1">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>A 4681-2024</t>
+          <t>A 4676-2024</t>
         </is>
       </c>
       <c r="B1001" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         </is>
       </c>
       <c r="G1001" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H1001" t="n">
         <v>0</v>
@@ -59019,14 +59019,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 4675-2024</t>
+          <t>A 4728-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -59083,7 +59083,7 @@
         <v>45329</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>45330</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45331</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45331</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45334</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59368,7 +59368,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59425,7 +59425,7 @@
         <v>45337</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59482,7 +59482,7 @@
         <v>45337</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59544,7 +59544,7 @@
         <v>45337</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>45338</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45341</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>45342</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>45345</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59829,7 +59829,7 @@
         <v>45345</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -569,7 +569,7 @@
         <v>43781</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43653</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44925</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45093</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>43406</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>43502</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>43514</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>43529</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43608</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43640</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43817</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>44284</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44298</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44305</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44344</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>44425</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>44952</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>44980</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44985</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>44998</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>45012</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45120</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45145</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45152</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45237</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45321</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>43319</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>43326</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>43333</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>43341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>43343</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>43347</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>43350</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>43353</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>43354</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43354</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43357</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43361</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43368</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43369</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43370</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43371</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43383</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43390</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43390</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43395</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>43395</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>43397</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>43397</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43397</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>43397</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>43397</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>43398</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>43399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>43401</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>43402</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>43409</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>43412</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>43412</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>43413</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>43416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>43419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>43419</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>43419</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>43422</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>43424</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>43424</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>43427</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>43431</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>43432</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>43437</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>43437</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>43439</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>43451</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>43451</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>43451</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>43451</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>43451</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>43451</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>43452</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>43455</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>43471</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>43473</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>43482</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>43485</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>43488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>43491</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>43491</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>43491</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>43501</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>43501</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>43503</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>43507</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>43511</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>43514</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>43514</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>43515</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>43518</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>43521</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>43521</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>43522</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>43529</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>43529</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43531</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43531</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43532</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>43534</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>43534</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>43537</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43537</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43538</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43544</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43548</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43552</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43558</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>43558</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>43563</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>43563</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43565</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>43570</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43572</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43572</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43573</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>43573</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>43573</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>43573</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43573</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43573</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43573</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>43580</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>43580</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>43581</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>43581</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>43600</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>43600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>43600</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>43601</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>43601</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>43605</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>43614</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>43619</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>43619</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>43619</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>43621</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>43627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>43627</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>43629</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43630</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43647</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43647</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43647</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43648</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43648</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43650</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43655</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43662</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43669</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43670</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43670</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43677</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43677</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>43678</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>43678</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>43681</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>43682</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>43682</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>43684</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43685</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43685</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43690</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43692</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43692</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>43692</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>43692</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>43697</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>43705</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>43711</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>43711</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>43712</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>43712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>43717</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>43718</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>43725</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>43725</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>43725</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>43726</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>43726</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>43727</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>43727</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>43730</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>43733</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>43741</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>43741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>43742</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>43745</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>43746</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>43746</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>43749</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43749</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>43752</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>43754</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>43755</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>43761</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>43761</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>43763</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43766</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>43766</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>43767</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>43767</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>43768</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>43770</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>43781</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>43781</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43781</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>43783</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>43783</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43787</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>43790</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>43803</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>43803</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>43804</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>43808</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>43811</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>43811</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>43811</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>43818</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>43822</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43822</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43832</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43833</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43837</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43847</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43850</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>43852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>43852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>43860</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>43874</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43878</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43878</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43880</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>43881</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>43889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>43895</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>43903</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>43906</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>43909</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>43914</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>43914</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>43915</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>43929</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>43930</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>43938</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>43950</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>43969</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43979</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43984</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43992</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43992</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43992</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44004</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44005</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44005</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44007</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44019</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44025</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44025</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44027</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44027</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44027</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44027</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44029</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44032</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44032</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44032</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44035</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44047</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44050</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44055</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44055</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44060</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44061</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44063</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44070</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44070</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44070</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>44070</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44075</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44076</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44077</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44077</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44078</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44084</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44088</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44088</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>44089</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>44095</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44096</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44102</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44103</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44104</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44104</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44104</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44106</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44106</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44119</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>44119</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44120</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>44127</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44127</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44127</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>44131</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44137</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44137</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44138</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44138</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44139</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44139</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44147</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>44152</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44154</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44158</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44159</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44159</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44181</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44187</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44203</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44203</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44206</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44207</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44209</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44215</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44215</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44216</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44216</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44218</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44218</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44232</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>44236</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>44238</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44238</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44239</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44245</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>44245</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>44246</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44249</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44253</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44257</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>44258</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44258</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44271</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44271</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>44273</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>44277</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>44278</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44279</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44279</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44284</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44284</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44284</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44286</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>44286</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44286</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44298</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44299</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44299</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44300</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44300</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44300</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44300</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44307</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44307</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44307</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44307</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44311</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44311</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44311</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44311</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>44312</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>44312</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>44314</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>44314</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>44316</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44319</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44326</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44329</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44340</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44341</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44343</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44343</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44343</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44361</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>44369</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44370</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44370</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>44371</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44374</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44375</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44378</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44385</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44386</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44386</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44414</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>44419</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44420</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>44420</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44420</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44420</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44421</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44421</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44425</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44427</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44432</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44432</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>44434</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>44434</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>44439</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44445</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44447</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44447</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44451</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44455</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44455</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44455</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44462</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44465</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44466</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44468</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44474</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44474</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44489</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44490</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44490</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44493</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44493</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44494</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>44494</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44494</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44501</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44501</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44503</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44504</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>44504</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>44510</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44532</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44553</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44558</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>44565</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44565</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>44565</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44565</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>44571</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>44576</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44579</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>44589</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44596</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44600</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44600</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44601</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44606</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44608</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>44608</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44609</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44615</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44616</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>44616</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44617</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>44617</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44617</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44617</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44627</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44627</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44630</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44630</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44630</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>44636</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>44637</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>44638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44645</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44649</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44651</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44655</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>44655</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44657</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44658</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>44676</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44687</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>44694</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>44694</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44713</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44713</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44721</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44722</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>44729</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>44739</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44739</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44748</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44750</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44753</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44753</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44753</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44754</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>44754</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>44756</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>44756</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44756</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44762</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44762</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44762</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44762</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44762</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44762</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44762</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44762</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44762</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>44762</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44762</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44762</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44774</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44775</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44775</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44790</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44798</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44806</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44806</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44806</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44806</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44812</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44817</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44817</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44819</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44822</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44825</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44825</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44825</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44825</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>44830</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>44830</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>44834</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>44848</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>44848</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44851</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44853</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44854</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>44860</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>44862</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44865</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>44872</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44872</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44880</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44880</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44882</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44882</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44884</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44886</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44888</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44890</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44890</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>44902</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>44902</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>44903</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>44908</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44916</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>44917</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>44917</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>44917</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>44925</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44925</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44925</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44937</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44938</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44939</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44944</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44944</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44945</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44950</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44956</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44956</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44956</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44957</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44966</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44966</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44966</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44966</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44966</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44969</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>44972</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44972</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>44973</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>44973</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44973</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44980</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44980</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44980</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44981</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44981</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44986</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44987</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44987</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44987</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44987</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44987</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44992</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44992</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44992</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44992</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45001</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45001</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45001</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45001</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45001</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45002</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45006</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45006</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45006</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45009</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45009</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45009</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45012</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45012</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45012</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45012</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45012</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45012</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45012</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45012</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45012</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45015</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45019</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45027</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45032</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45036</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45040</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45041</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45042</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45043</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45043</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45048</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45049</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45049</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45049</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45050</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45051</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45053</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45056</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45057</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45057</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45058</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45058</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45061</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45061</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45061</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45061</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45062</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45063</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45069</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>45070</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45071</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45071</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45072</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45072</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>45072</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45072</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45075</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45075</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45076</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>45078</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45084</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45085</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45086</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45090</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45090</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45091</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45091</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45093</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>45096</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45097</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45099</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45099</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45103</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45103</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45103</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45103</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45104</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>45104</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45104</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45105</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45104</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45104</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45104</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45105</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45105</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45106</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45106</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45106</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45110</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45110</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45115</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45117</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45118</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45118</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45118</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45118</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45118</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>45118</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>45119</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45119</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45119</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45120</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45121</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45128</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45138</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45139</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45139</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45139</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45139</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>45139</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50094,7 +50094,7 @@
         <v>45140</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45152</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45163</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>45166</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45166</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45166</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45168</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45169</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>45169</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45169</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45169</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45171</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45171</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45172</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45178</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45178</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45178</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>45178</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>45188</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45188</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45188</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45189</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45189</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45190</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45191</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45191</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45192</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45193</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45194</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45194</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45194</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45194</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45194</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45194</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45194</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45194</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45194</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45194</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45195</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45195</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45195</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>45195</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45195</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45195</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45196</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>45196</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45196</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45196</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         <v>45197</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>45197</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45199</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45199</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45201</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45201</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45201</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45201</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45203</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45211</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45211</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45222</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45223</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45226</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45226</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45229</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45230</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45236</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45236</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45236</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45237</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45238</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45238</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45238</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45239</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45247</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45251</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45251</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45253</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45253</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45253</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45253</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45257</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45257</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45257</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45259</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56042,7 +56042,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>45268</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45271</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>45272</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>45275</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45278</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45278</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45280</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45280</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45280</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45280</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45280</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45280</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45280</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45280</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45280</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45280</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45282</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45285</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45296</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45299</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57430,7 +57430,7 @@
         <v>45299</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57544,7 +57544,7 @@
         <v>45299</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45301</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45302</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>45303</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45303</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45303</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45303</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45307</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45307</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45310</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@